--- a/ONCHO/Entomological survey Survey/Nigeria/2026/delta/ng_oncho_2605_2_river_inspection_del.xlsx
+++ b/ONCHO/Entomological survey Survey/Nigeria/2026/delta/ng_oncho_2605_2_river_inspection_del.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Entomological survey Survey\Nigeria\2026\delta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0030A5C6-D87B-4F30-B899-095426F6829D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{828A8796-832B-4402-AD26-9B6CB1499821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -532,12 +532,6 @@
     <t>community = ${r_community}</t>
   </si>
   <si>
-    <t>ng_oncho_2605_2_river_inspection_del</t>
-  </si>
-  <si>
-    <t>(2026 Delta) 2. River inspection Form</t>
-  </si>
-  <si>
     <t>ABIA</t>
   </si>
   <si>
@@ -1652,6 +1646,12 @@
   </si>
   <si>
     <t>ABI_ARO_E_055</t>
+  </si>
+  <si>
+    <t>(2026 - Delta, Anambra, Abia) 2. River inspection Form</t>
+  </si>
+  <si>
+    <t>ng_oncho_2605_2_river_inspection_del_v2</t>
   </si>
 </sst>
 </file>
@@ -1846,17 +1846,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3344,10 +3334,10 @@
         <v>107</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -3355,10 +3345,10 @@
         <v>107</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -3366,10 +3356,10 @@
         <v>107</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -3381,13 +3371,13 @@
         <v>106</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D36" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -3395,13 +3385,13 @@
         <v>106</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D37" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -3409,13 +3399,13 @@
         <v>106</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D38" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -3423,13 +3413,13 @@
         <v>106</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D39" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -3437,13 +3427,13 @@
         <v>106</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D40" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -3451,13 +3441,13 @@
         <v>106</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D41" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -3465,13 +3455,13 @@
         <v>106</v>
       </c>
       <c r="B42" s="21" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D42" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -3479,13 +3469,13 @@
         <v>106</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D43" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -3493,13 +3483,13 @@
         <v>106</v>
       </c>
       <c r="B44" s="21" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D44" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -3507,13 +3497,13 @@
         <v>106</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D45" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -3521,13 +3511,13 @@
         <v>106</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D46" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -3535,13 +3525,13 @@
         <v>106</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C47" s="21" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D47" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -3549,13 +3539,13 @@
         <v>106</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D48" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -3563,13 +3553,13 @@
         <v>106</v>
       </c>
       <c r="B49" s="21" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D49" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -3577,13 +3567,13 @@
         <v>106</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D50" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -3591,13 +3581,13 @@
         <v>106</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D51" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -3605,13 +3595,13 @@
         <v>106</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D52" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -3619,13 +3609,13 @@
         <v>106</v>
       </c>
       <c r="B53" s="21" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D53" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -3633,13 +3623,13 @@
         <v>106</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D54" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -3647,13 +3637,13 @@
         <v>106</v>
       </c>
       <c r="B55" s="21" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C55" s="21" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D55" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -3661,13 +3651,13 @@
         <v>106</v>
       </c>
       <c r="B56" s="21" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C56" s="21" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D56" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -3675,13 +3665,13 @@
         <v>106</v>
       </c>
       <c r="B57" s="21" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C57" s="21" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D57" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -3689,13 +3679,13 @@
         <v>106</v>
       </c>
       <c r="B58" s="21" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D58" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -3703,13 +3693,13 @@
         <v>106</v>
       </c>
       <c r="B59" s="21" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C59" s="21" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D59" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -3717,13 +3707,13 @@
         <v>106</v>
       </c>
       <c r="B60" s="21" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D60" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -3731,13 +3721,13 @@
         <v>106</v>
       </c>
       <c r="B61" s="21" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C61" s="21" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D61" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -3745,13 +3735,13 @@
         <v>106</v>
       </c>
       <c r="B62" s="21" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D62" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -3759,13 +3749,13 @@
         <v>106</v>
       </c>
       <c r="B63" s="21" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C63" s="21" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D63" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -3773,13 +3763,13 @@
         <v>106</v>
       </c>
       <c r="B64" s="21" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C64" s="21" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D64" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -3787,13 +3777,13 @@
         <v>106</v>
       </c>
       <c r="B65" s="21" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D65" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -3801,13 +3791,13 @@
         <v>106</v>
       </c>
       <c r="B66" s="21" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C66" s="21" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D66" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -3815,13 +3805,13 @@
         <v>106</v>
       </c>
       <c r="B67" s="21" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C67" s="21" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D67" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -3829,13 +3819,13 @@
         <v>106</v>
       </c>
       <c r="B68" s="21" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D68" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -3843,13 +3833,13 @@
         <v>106</v>
       </c>
       <c r="B69" s="21" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C69" s="21" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D69" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -3857,13 +3847,13 @@
         <v>106</v>
       </c>
       <c r="B70" s="21" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C70" s="21" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D70" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3871,13 +3861,13 @@
         <v>106</v>
       </c>
       <c r="B71" s="21" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C71" s="21" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D71" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -3885,13 +3875,13 @@
         <v>106</v>
       </c>
       <c r="B72" s="21" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C72" s="21" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D72" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3899,13 +3889,13 @@
         <v>106</v>
       </c>
       <c r="B73" s="21" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C73" s="21" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D73" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -3913,13 +3903,13 @@
         <v>106</v>
       </c>
       <c r="B74" s="21" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C74" s="21" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D74" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3927,13 +3917,13 @@
         <v>106</v>
       </c>
       <c r="B75" s="21" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C75" s="21" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D75" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -3941,13 +3931,13 @@
         <v>106</v>
       </c>
       <c r="B76" s="21" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C76" s="21" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D76" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -3960,13 +3950,13 @@
         <v>155</v>
       </c>
       <c r="B78" s="21" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E78" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
@@ -3974,13 +3964,13 @@
         <v>155</v>
       </c>
       <c r="B79" s="21" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C79" s="21" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E79" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -3988,13 +3978,13 @@
         <v>155</v>
       </c>
       <c r="B80" s="21" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C80" s="21" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E80" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -4002,13 +3992,13 @@
         <v>155</v>
       </c>
       <c r="B81" s="21" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C81" s="21" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E81" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -4016,13 +4006,13 @@
         <v>155</v>
       </c>
       <c r="B82" s="21" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C82" s="21" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E82" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4030,13 +4020,13 @@
         <v>155</v>
       </c>
       <c r="B83" s="21" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C83" s="21" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E83" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -4044,13 +4034,13 @@
         <v>155</v>
       </c>
       <c r="B84" s="21" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C84" s="21" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E84" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4058,13 +4048,13 @@
         <v>155</v>
       </c>
       <c r="B85" s="21" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C85" s="21" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E85" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -4072,13 +4062,13 @@
         <v>155</v>
       </c>
       <c r="B86" s="21" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C86" s="21" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E86" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -4086,13 +4076,13 @@
         <v>155</v>
       </c>
       <c r="B87" s="21" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C87" s="21" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E87" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
@@ -4100,13 +4090,13 @@
         <v>155</v>
       </c>
       <c r="B88" s="21" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C88" s="21" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E88" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4114,13 +4104,13 @@
         <v>155</v>
       </c>
       <c r="B89" s="21" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C89" s="21" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E89" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
@@ -4128,13 +4118,13 @@
         <v>155</v>
       </c>
       <c r="B90" s="21" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C90" s="21" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E90" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -4142,13 +4132,13 @@
         <v>155</v>
       </c>
       <c r="B91" s="21" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C91" s="21" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E91" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -4156,13 +4146,13 @@
         <v>155</v>
       </c>
       <c r="B92" s="21" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C92" s="21" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E92" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -4170,13 +4160,13 @@
         <v>155</v>
       </c>
       <c r="B93" s="21" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C93" s="21" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E93" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -4184,13 +4174,13 @@
         <v>155</v>
       </c>
       <c r="B94" s="21" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C94" s="21" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E94" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4198,13 +4188,13 @@
         <v>155</v>
       </c>
       <c r="B95" s="21" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C95" s="21" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E95" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -4212,13 +4202,13 @@
         <v>155</v>
       </c>
       <c r="B96" s="21" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C96" s="21" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E96" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -4226,13 +4216,13 @@
         <v>155</v>
       </c>
       <c r="B97" s="21" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C97" s="21" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E97" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -4240,13 +4230,13 @@
         <v>155</v>
       </c>
       <c r="B98" s="21" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C98" s="21" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E98" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4254,13 +4244,13 @@
         <v>155</v>
       </c>
       <c r="B99" s="21" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C99" s="21" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E99" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -4268,13 +4258,13 @@
         <v>155</v>
       </c>
       <c r="B100" s="21" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C100" s="21" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E100" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4282,13 +4272,13 @@
         <v>155</v>
       </c>
       <c r="B101" s="21" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C101" s="21" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E101" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -4296,13 +4286,13 @@
         <v>155</v>
       </c>
       <c r="B102" s="21" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C102" s="21" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E102" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -4310,13 +4300,13 @@
         <v>155</v>
       </c>
       <c r="B103" s="21" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C103" s="21" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E103" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -4324,13 +4314,13 @@
         <v>155</v>
       </c>
       <c r="B104" s="21" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C104" s="21" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E104" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -4338,13 +4328,13 @@
         <v>155</v>
       </c>
       <c r="B105" s="21" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C105" s="21" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E105" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -4352,13 +4342,13 @@
         <v>155</v>
       </c>
       <c r="B106" s="21" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C106" s="21" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E106" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -4366,13 +4356,13 @@
         <v>155</v>
       </c>
       <c r="B107" s="21" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C107" s="21" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E107" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -4380,13 +4370,13 @@
         <v>155</v>
       </c>
       <c r="B108" s="21" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C108" s="21" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E108" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4394,13 +4384,13 @@
         <v>155</v>
       </c>
       <c r="B109" s="21" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C109" s="21" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E109" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
@@ -4408,13 +4398,13 @@
         <v>155</v>
       </c>
       <c r="B110" s="21" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C110" s="21" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E110" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
@@ -4422,13 +4412,13 @@
         <v>155</v>
       </c>
       <c r="B111" s="21" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C111" s="21" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E111" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
@@ -4436,13 +4426,13 @@
         <v>155</v>
       </c>
       <c r="B112" s="21" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C112" s="21" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E112" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -4450,13 +4440,13 @@
         <v>155</v>
       </c>
       <c r="B113" s="21" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C113" s="21" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E113" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4464,13 +4454,13 @@
         <v>155</v>
       </c>
       <c r="B114" s="21" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C114" s="21" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E114" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -4478,13 +4468,13 @@
         <v>155</v>
       </c>
       <c r="B115" s="21" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C115" s="21" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E115" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -4492,13 +4482,13 @@
         <v>155</v>
       </c>
       <c r="B116" s="21" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C116" s="21" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E116" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -4506,13 +4496,13 @@
         <v>155</v>
       </c>
       <c r="B117" s="21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C117" s="21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E117" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4520,13 +4510,13 @@
         <v>155</v>
       </c>
       <c r="B118" s="21" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C118" s="21" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E118" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -4534,13 +4524,13 @@
         <v>155</v>
       </c>
       <c r="B119" s="21" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C119" s="21" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E119" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
@@ -4548,13 +4538,13 @@
         <v>155</v>
       </c>
       <c r="B120" s="21" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C120" s="21" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E120" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
@@ -4562,13 +4552,13 @@
         <v>155</v>
       </c>
       <c r="B121" s="21" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C121" s="21" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E121" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
@@ -4576,13 +4566,13 @@
         <v>155</v>
       </c>
       <c r="B122" s="21" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C122" s="21" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E122" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
@@ -4590,13 +4580,13 @@
         <v>155</v>
       </c>
       <c r="B123" s="21" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C123" s="21" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E123" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
@@ -4604,13 +4594,13 @@
         <v>155</v>
       </c>
       <c r="B124" s="21" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C124" s="21" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E124" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
@@ -4618,13 +4608,13 @@
         <v>155</v>
       </c>
       <c r="B125" s="21" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C125" s="21" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E125" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
@@ -4632,13 +4622,13 @@
         <v>155</v>
       </c>
       <c r="B126" s="21" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C126" s="21" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E126" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
@@ -4646,13 +4636,13 @@
         <v>155</v>
       </c>
       <c r="B127" s="21" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C127" s="21" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E127" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
@@ -4660,13 +4650,13 @@
         <v>155</v>
       </c>
       <c r="B128" s="21" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C128" s="21" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E128" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4674,13 +4664,13 @@
         <v>155</v>
       </c>
       <c r="B129" s="21" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C129" s="21" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E129" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
@@ -4688,13 +4678,13 @@
         <v>155</v>
       </c>
       <c r="B130" s="21" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C130" s="21" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E130" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
@@ -4702,13 +4692,13 @@
         <v>155</v>
       </c>
       <c r="B131" s="21" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C131" s="21" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E131" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
@@ -4716,13 +4706,13 @@
         <v>155</v>
       </c>
       <c r="B132" s="21" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C132" s="21" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E132" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -4730,13 +4720,13 @@
         <v>155</v>
       </c>
       <c r="B133" s="21" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C133" s="21" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E133" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -4744,13 +4734,13 @@
         <v>155</v>
       </c>
       <c r="B134" s="21" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C134" s="21" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E134" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
@@ -4758,13 +4748,13 @@
         <v>155</v>
       </c>
       <c r="B135" s="21" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C135" s="21" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E135" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4772,13 +4762,13 @@
         <v>155</v>
       </c>
       <c r="B136" s="21" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C136" s="21" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E136" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -4786,13 +4776,13 @@
         <v>155</v>
       </c>
       <c r="B137" s="21" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C137" s="21" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E137" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
@@ -4800,13 +4790,13 @@
         <v>155</v>
       </c>
       <c r="B138" s="21" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C138" s="21" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E138" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
@@ -4814,13 +4804,13 @@
         <v>155</v>
       </c>
       <c r="B139" s="21" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C139" s="21" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E139" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -4828,13 +4818,13 @@
         <v>155</v>
       </c>
       <c r="B140" s="21" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C140" s="21" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E140" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
@@ -4842,13 +4832,13 @@
         <v>155</v>
       </c>
       <c r="B141" s="21" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C141" s="21" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E141" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
@@ -4856,13 +4846,13 @@
         <v>155</v>
       </c>
       <c r="B142" s="21" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C142" s="21" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E142" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
@@ -4870,13 +4860,13 @@
         <v>155</v>
       </c>
       <c r="B143" s="21" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C143" s="21" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E143" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
@@ -4884,13 +4874,13 @@
         <v>155</v>
       </c>
       <c r="B144" s="21" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C144" s="21" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E144" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -4898,13 +4888,13 @@
         <v>155</v>
       </c>
       <c r="B145" s="21" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C145" s="21" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E145" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
@@ -4912,13 +4902,13 @@
         <v>155</v>
       </c>
       <c r="B146" s="21" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C146" s="21" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E146" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
@@ -4926,13 +4916,13 @@
         <v>155</v>
       </c>
       <c r="B147" s="21" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C147" s="21" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E147" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
@@ -4940,13 +4930,13 @@
         <v>155</v>
       </c>
       <c r="B148" s="21" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C148" s="21" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E148" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
@@ -4954,13 +4944,13 @@
         <v>155</v>
       </c>
       <c r="B149" s="21" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C149" s="21" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E149" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
@@ -4968,13 +4958,13 @@
         <v>155</v>
       </c>
       <c r="B150" s="21" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C150" s="21" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E150" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
@@ -4982,13 +4972,13 @@
         <v>155</v>
       </c>
       <c r="B151" s="21" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C151" s="21" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E151" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
@@ -4996,13 +4986,13 @@
         <v>155</v>
       </c>
       <c r="B152" s="21" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C152" s="21" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E152" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
@@ -5010,13 +5000,13 @@
         <v>155</v>
       </c>
       <c r="B153" s="21" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C153" s="21" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E153" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
@@ -5024,13 +5014,13 @@
         <v>155</v>
       </c>
       <c r="B154" s="21" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C154" s="21" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E154" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -5038,13 +5028,13 @@
         <v>155</v>
       </c>
       <c r="B155" s="21" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C155" s="21" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E155" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
@@ -5052,13 +5042,13 @@
         <v>155</v>
       </c>
       <c r="B156" s="21" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C156" s="21" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E156" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
@@ -5066,13 +5056,13 @@
         <v>155</v>
       </c>
       <c r="B157" s="21" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C157" s="21" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E157" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
@@ -5080,13 +5070,13 @@
         <v>155</v>
       </c>
       <c r="B158" s="21" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C158" s="21" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E158" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
@@ -5094,13 +5084,13 @@
         <v>155</v>
       </c>
       <c r="B159" s="21" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C159" s="21" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E159" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
@@ -5108,13 +5098,13 @@
         <v>155</v>
       </c>
       <c r="B160" s="21" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C160" s="21" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E160" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
@@ -5122,13 +5112,13 @@
         <v>155</v>
       </c>
       <c r="B161" s="21" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C161" s="21" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E161" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
@@ -5136,13 +5126,13 @@
         <v>155</v>
       </c>
       <c r="B162" s="21" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C162" s="21" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E162" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
@@ -5150,13 +5140,13 @@
         <v>155</v>
       </c>
       <c r="B163" s="21" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C163" s="21" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E163" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -5164,13 +5154,13 @@
         <v>155</v>
       </c>
       <c r="B164" s="21" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C164" s="21" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E164" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
@@ -5178,13 +5168,13 @@
         <v>155</v>
       </c>
       <c r="B165" s="21" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C165" s="21" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E165" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
@@ -5192,13 +5182,13 @@
         <v>155</v>
       </c>
       <c r="B166" s="21" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C166" s="21" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E166" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -5206,13 +5196,13 @@
         <v>155</v>
       </c>
       <c r="B167" s="21" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C167" s="21" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E167" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
@@ -5220,13 +5210,13 @@
         <v>155</v>
       </c>
       <c r="B168" s="21" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C168" s="21" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E168" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
@@ -5234,13 +5224,13 @@
         <v>155</v>
       </c>
       <c r="B169" s="21" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C169" s="21" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E169" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -5248,13 +5238,13 @@
         <v>155</v>
       </c>
       <c r="B170" s="21" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C170" s="21" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E170" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
@@ -5262,13 +5252,13 @@
         <v>155</v>
       </c>
       <c r="B171" s="21" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C171" s="21" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E171" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
@@ -5276,13 +5266,13 @@
         <v>155</v>
       </c>
       <c r="B172" s="21" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C172" s="21" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E172" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
@@ -5290,13 +5280,13 @@
         <v>155</v>
       </c>
       <c r="B173" s="21" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C173" s="21" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E173" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
@@ -5304,13 +5294,13 @@
         <v>155</v>
       </c>
       <c r="B174" s="21" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C174" s="21" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E174" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
@@ -5318,13 +5308,13 @@
         <v>155</v>
       </c>
       <c r="B175" s="21" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C175" s="21" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E175" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
@@ -5332,13 +5322,13 @@
         <v>155</v>
       </c>
       <c r="B176" s="21" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C176" s="21" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E176" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
@@ -5346,13 +5336,13 @@
         <v>155</v>
       </c>
       <c r="B177" s="21" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C177" s="21" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E177" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
@@ -5360,13 +5350,13 @@
         <v>155</v>
       </c>
       <c r="B178" s="21" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C178" s="21" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E178" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -5374,13 +5364,13 @@
         <v>155</v>
       </c>
       <c r="B179" s="21" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C179" s="21" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E179" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
@@ -5388,13 +5378,13 @@
         <v>155</v>
       </c>
       <c r="B180" s="21" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C180" s="21" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E180" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
@@ -5402,13 +5392,13 @@
         <v>155</v>
       </c>
       <c r="B181" s="21" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C181" s="21" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E181" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
@@ -5416,13 +5406,13 @@
         <v>155</v>
       </c>
       <c r="B182" s="21" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C182" s="21" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E182" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
@@ -5430,13 +5420,13 @@
         <v>155</v>
       </c>
       <c r="B183" s="21" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C183" s="21" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E183" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
@@ -5444,13 +5434,13 @@
         <v>155</v>
       </c>
       <c r="B184" s="21" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C184" s="21" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E184" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="185" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -5458,13 +5448,13 @@
         <v>155</v>
       </c>
       <c r="B185" s="21" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C185" s="21" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E185" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
@@ -5472,13 +5462,13 @@
         <v>155</v>
       </c>
       <c r="B186" s="21" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C186" s="21" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E186" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
@@ -5486,13 +5476,13 @@
         <v>155</v>
       </c>
       <c r="B187" s="21" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C187" s="21" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E187" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="188" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -5500,13 +5490,13 @@
         <v>155</v>
       </c>
       <c r="B188" s="21" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C188" s="21" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E188" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
@@ -5514,13 +5504,13 @@
         <v>155</v>
       </c>
       <c r="B189" s="21" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C189" s="21" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E189" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
@@ -5528,13 +5518,13 @@
         <v>155</v>
       </c>
       <c r="B190" s="21" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C190" s="21" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E190" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
@@ -5542,13 +5532,13 @@
         <v>155</v>
       </c>
       <c r="B191" s="21" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C191" s="21" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E191" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -5556,13 +5546,13 @@
         <v>155</v>
       </c>
       <c r="B192" s="21" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C192" s="21" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E192" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
@@ -5570,13 +5560,13 @@
         <v>155</v>
       </c>
       <c r="B193" s="21" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C193" s="21" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E193" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="194" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -5584,13 +5574,13 @@
         <v>155</v>
       </c>
       <c r="B194" s="21" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C194" s="21" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E194" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
@@ -5598,13 +5588,13 @@
         <v>155</v>
       </c>
       <c r="B195" s="21" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C195" s="21" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E195" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="196" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -5612,13 +5602,13 @@
         <v>155</v>
       </c>
       <c r="B196" s="21" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C196" s="21" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E196" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="197" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -5626,13 +5616,13 @@
         <v>155</v>
       </c>
       <c r="B197" s="21" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C197" s="21" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E197" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
@@ -5640,13 +5630,13 @@
         <v>155</v>
       </c>
       <c r="B198" s="21" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C198" s="21" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E198" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="199" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -5654,13 +5644,13 @@
         <v>155</v>
       </c>
       <c r="B199" s="21" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C199" s="21" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E199" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
@@ -5668,13 +5658,13 @@
         <v>155</v>
       </c>
       <c r="B200" s="21" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C200" s="21" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E200" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="201" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -5682,13 +5672,13 @@
         <v>155</v>
       </c>
       <c r="B201" s="21" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C201" s="21" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E201" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
@@ -5696,13 +5686,13 @@
         <v>155</v>
       </c>
       <c r="B202" s="21" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C202" s="21" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E202" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
@@ -5710,13 +5700,13 @@
         <v>155</v>
       </c>
       <c r="B203" s="21" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C203" s="21" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E203" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
@@ -5724,13 +5714,13 @@
         <v>155</v>
       </c>
       <c r="B204" s="21" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C204" s="21" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E204" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
@@ -5738,13 +5728,13 @@
         <v>155</v>
       </c>
       <c r="B205" s="21" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C205" s="21" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E205" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="206" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -5752,13 +5742,13 @@
         <v>155</v>
       </c>
       <c r="B206" s="21" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C206" s="21" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E206" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="207" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -5766,13 +5756,13 @@
         <v>155</v>
       </c>
       <c r="B207" s="21" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C207" s="21" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E207" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
@@ -5780,13 +5770,13 @@
         <v>155</v>
       </c>
       <c r="B208" s="21" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C208" s="21" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E208" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
@@ -5794,13 +5784,13 @@
         <v>155</v>
       </c>
       <c r="B209" s="21" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C209" s="21" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E209" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="210" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -5808,13 +5798,13 @@
         <v>155</v>
       </c>
       <c r="B210" s="21" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C210" s="21" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E210" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
@@ -5822,13 +5812,13 @@
         <v>155</v>
       </c>
       <c r="B211" s="21" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C211" s="21" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E211" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
@@ -5836,13 +5826,13 @@
         <v>155</v>
       </c>
       <c r="B212" s="21" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C212" s="21" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E212" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
@@ -5850,13 +5840,13 @@
         <v>155</v>
       </c>
       <c r="B213" s="21" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C213" s="21" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E213" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
@@ -5864,13 +5854,13 @@
         <v>155</v>
       </c>
       <c r="B214" s="21" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C214" s="21" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E214" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="215" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -5878,13 +5868,13 @@
         <v>155</v>
       </c>
       <c r="B215" s="21" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C215" s="21" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E215" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
@@ -5892,13 +5882,13 @@
         <v>155</v>
       </c>
       <c r="B216" s="21" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C216" s="21" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E216" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
@@ -5906,13 +5896,13 @@
         <v>155</v>
       </c>
       <c r="B217" s="21" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C217" s="21" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E217" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
@@ -5920,13 +5910,13 @@
         <v>155</v>
       </c>
       <c r="B218" s="21" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C218" s="21" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E218" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
@@ -5934,13 +5924,13 @@
         <v>155</v>
       </c>
       <c r="B219" s="21" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C219" s="21" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E219" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
@@ -5948,13 +5938,13 @@
         <v>155</v>
       </c>
       <c r="B220" s="21" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C220" s="21" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E220" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
@@ -5962,13 +5952,13 @@
         <v>155</v>
       </c>
       <c r="B221" s="21" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C221" s="21" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E221" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="222" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -5976,13 +5966,13 @@
         <v>155</v>
       </c>
       <c r="B222" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C222" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E222" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
@@ -5990,13 +5980,13 @@
         <v>155</v>
       </c>
       <c r="B223" s="21" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C223" s="21" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E223" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="224" spans="1:5" ht="63" x14ac:dyDescent="0.25">
@@ -6004,13 +5994,13 @@
         <v>155</v>
       </c>
       <c r="B224" s="21" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C224" s="21" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E224" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
@@ -6018,13 +6008,13 @@
         <v>155</v>
       </c>
       <c r="B225" s="21" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C225" s="21" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E225" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
@@ -6032,13 +6022,13 @@
         <v>155</v>
       </c>
       <c r="B226" s="21" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C226" s="21" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E226" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
@@ -6046,13 +6036,13 @@
         <v>155</v>
       </c>
       <c r="B227" s="21" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C227" s="21" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E227" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
@@ -6060,13 +6050,13 @@
         <v>155</v>
       </c>
       <c r="B228" s="21" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C228" s="21" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E228" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
@@ -6074,13 +6064,13 @@
         <v>155</v>
       </c>
       <c r="B229" s="21" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C229" s="21" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E229" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
@@ -6088,13 +6078,13 @@
         <v>155</v>
       </c>
       <c r="B230" s="21" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C230" s="21" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E230" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
@@ -6102,13 +6092,13 @@
         <v>155</v>
       </c>
       <c r="B231" s="21" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C231" s="21" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E231" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
@@ -6116,13 +6106,13 @@
         <v>155</v>
       </c>
       <c r="B232" s="21" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C232" s="21" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E232" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
@@ -6130,13 +6120,13 @@
         <v>155</v>
       </c>
       <c r="B233" s="21" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C233" s="21" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E233" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
@@ -6144,13 +6134,13 @@
         <v>155</v>
       </c>
       <c r="B234" s="21" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C234" s="21" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E234" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
@@ -6158,13 +6148,13 @@
         <v>155</v>
       </c>
       <c r="B235" s="21" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C235" s="21" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E235" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
@@ -6172,13 +6162,13 @@
         <v>155</v>
       </c>
       <c r="B236" s="21" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C236" s="21" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E236" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
@@ -6186,13 +6176,13 @@
         <v>155</v>
       </c>
       <c r="B237" s="21" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C237" s="21" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E237" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
@@ -6200,13 +6190,13 @@
         <v>155</v>
       </c>
       <c r="B238" s="21" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C238" s="21" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E238" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="239" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -6214,13 +6204,13 @@
         <v>155</v>
       </c>
       <c r="B239" s="21" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C239" s="21" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E239" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="240" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -6228,13 +6218,13 @@
         <v>155</v>
       </c>
       <c r="B240" s="21" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C240" s="21" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E240" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -6242,13 +6232,13 @@
         <v>155</v>
       </c>
       <c r="B241" s="21" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C241" s="21" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E241" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -6260,13 +6250,13 @@
         <v>38</v>
       </c>
       <c r="B243" s="21" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C243" s="21" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F243" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -6274,13 +6264,13 @@
         <v>38</v>
       </c>
       <c r="B244" s="21" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C244" s="21" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F244" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -6288,13 +6278,13 @@
         <v>38</v>
       </c>
       <c r="B245" s="21" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C245" s="21" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F245" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -6302,13 +6292,13 @@
         <v>38</v>
       </c>
       <c r="B246" s="21" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C246" s="21" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F246" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -6316,13 +6306,13 @@
         <v>38</v>
       </c>
       <c r="B247" s="21" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C247" s="21" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F247" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -6330,13 +6320,13 @@
         <v>38</v>
       </c>
       <c r="B248" s="21" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C248" s="21" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F248" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -6344,13 +6334,13 @@
         <v>38</v>
       </c>
       <c r="B249" s="21" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C249" s="21" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F249" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -6358,13 +6348,13 @@
         <v>38</v>
       </c>
       <c r="B250" s="21" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C250" s="21" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F250" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -6372,13 +6362,13 @@
         <v>38</v>
       </c>
       <c r="B251" s="21" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C251" s="21" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F251" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -6386,13 +6376,13 @@
         <v>38</v>
       </c>
       <c r="B252" s="21" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C252" s="21" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F252" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -6400,13 +6390,13 @@
         <v>38</v>
       </c>
       <c r="B253" s="21" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C253" s="21" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F253" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -6414,13 +6404,13 @@
         <v>38</v>
       </c>
       <c r="B254" s="21" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C254" s="21" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F254" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -6428,13 +6418,13 @@
         <v>38</v>
       </c>
       <c r="B255" s="21" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C255" s="21" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F255" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -6442,13 +6432,13 @@
         <v>38</v>
       </c>
       <c r="B256" s="21" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C256" s="21" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F256" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -6456,13 +6446,13 @@
         <v>38</v>
       </c>
       <c r="B257" s="21" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C257" s="21" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F257" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -6470,13 +6460,13 @@
         <v>38</v>
       </c>
       <c r="B258" s="21" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C258" s="21" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F258" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -6484,13 +6474,13 @@
         <v>38</v>
       </c>
       <c r="B259" s="21" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C259" s="21" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F259" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -6498,13 +6488,13 @@
         <v>38</v>
       </c>
       <c r="B260" s="21" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C260" s="21" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F260" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -6512,13 +6502,13 @@
         <v>38</v>
       </c>
       <c r="B261" s="21" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C261" s="21" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F261" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -6526,13 +6516,13 @@
         <v>38</v>
       </c>
       <c r="B262" s="21" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C262" s="21" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="F262" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -6540,13 +6530,13 @@
         <v>38</v>
       </c>
       <c r="B263" s="21" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C263" s="21" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F263" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -6554,13 +6544,13 @@
         <v>38</v>
       </c>
       <c r="B264" s="21" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C264" s="21" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F264" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -6568,13 +6558,13 @@
         <v>38</v>
       </c>
       <c r="B265" s="21" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C265" s="21" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F265" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -6582,13 +6572,13 @@
         <v>38</v>
       </c>
       <c r="B266" s="21" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C266" s="21" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="F266" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -6596,13 +6586,13 @@
         <v>38</v>
       </c>
       <c r="B267" s="21" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C267" s="21" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F267" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -6610,13 +6600,13 @@
         <v>38</v>
       </c>
       <c r="B268" s="21" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C268" s="21" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F268" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -6624,13 +6614,13 @@
         <v>38</v>
       </c>
       <c r="B269" s="21" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C269" s="21" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F269" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -6638,13 +6628,13 @@
         <v>38</v>
       </c>
       <c r="B270" s="21" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C270" s="21" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F270" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -6652,13 +6642,13 @@
         <v>38</v>
       </c>
       <c r="B271" s="21" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C271" s="21" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F271" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -6666,13 +6656,13 @@
         <v>38</v>
       </c>
       <c r="B272" s="21" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C272" s="21" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F272" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -6680,13 +6670,13 @@
         <v>38</v>
       </c>
       <c r="B273" s="21" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C273" s="21" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F273" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -6694,13 +6684,13 @@
         <v>38</v>
       </c>
       <c r="B274" s="21" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C274" s="21" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F274" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -6708,13 +6698,13 @@
         <v>38</v>
       </c>
       <c r="B275" s="21" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C275" s="21" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F275" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -6722,13 +6712,13 @@
         <v>38</v>
       </c>
       <c r="B276" s="21" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C276" s="21" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="F276" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -6736,13 +6726,13 @@
         <v>38</v>
       </c>
       <c r="B277" s="21" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C277" s="21" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="F277" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -6750,13 +6740,13 @@
         <v>38</v>
       </c>
       <c r="B278" s="21" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C278" s="21" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F278" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -6764,13 +6754,13 @@
         <v>38</v>
       </c>
       <c r="B279" s="21" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C279" s="21" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="F279" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -6778,13 +6768,13 @@
         <v>38</v>
       </c>
       <c r="B280" s="21" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C280" s="21" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F280" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -6792,13 +6782,13 @@
         <v>38</v>
       </c>
       <c r="B281" s="21" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C281" s="21" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="F281" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -6806,13 +6796,13 @@
         <v>38</v>
       </c>
       <c r="B282" s="21" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C282" s="21" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="F282" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -6820,13 +6810,13 @@
         <v>38</v>
       </c>
       <c r="B283" s="21" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C283" s="21" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="F283" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -6834,13 +6824,13 @@
         <v>38</v>
       </c>
       <c r="B284" s="21" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C284" s="21" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="F284" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -6848,13 +6838,13 @@
         <v>38</v>
       </c>
       <c r="B285" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C285" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="F285" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -6862,13 +6852,13 @@
         <v>38</v>
       </c>
       <c r="B286" s="21" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C286" s="21" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="F286" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -6876,13 +6866,13 @@
         <v>38</v>
       </c>
       <c r="B287" s="21" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C287" s="21" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F287" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -6890,13 +6880,13 @@
         <v>38</v>
       </c>
       <c r="B288" s="21" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C288" s="21" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F288" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -6904,13 +6894,13 @@
         <v>38</v>
       </c>
       <c r="B289" s="21" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C289" s="21" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F289" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -6918,13 +6908,13 @@
         <v>38</v>
       </c>
       <c r="B290" s="21" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C290" s="21" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F290" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -6932,13 +6922,13 @@
         <v>38</v>
       </c>
       <c r="B291" s="21" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C291" s="21" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F291" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -6946,13 +6936,13 @@
         <v>38</v>
       </c>
       <c r="B292" s="21" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C292" s="21" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="F292" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -6960,13 +6950,13 @@
         <v>38</v>
       </c>
       <c r="B293" s="21" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C293" s="21" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F293" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -6974,13 +6964,13 @@
         <v>38</v>
       </c>
       <c r="B294" s="21" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C294" s="21" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="F294" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -6988,13 +6978,13 @@
         <v>38</v>
       </c>
       <c r="B295" s="21" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C295" s="21" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="F295" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -7002,13 +6992,13 @@
         <v>38</v>
       </c>
       <c r="B296" s="21" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C296" s="21" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F296" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -7016,13 +7006,13 @@
         <v>38</v>
       </c>
       <c r="B297" s="21" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C297" s="21" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="F297" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -7030,13 +7020,13 @@
         <v>38</v>
       </c>
       <c r="B298" s="21" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C298" s="21" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="F298" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -7044,13 +7034,13 @@
         <v>38</v>
       </c>
       <c r="B299" s="21" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C299" s="21" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="F299" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -7058,13 +7048,13 @@
         <v>38</v>
       </c>
       <c r="B300" s="21" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C300" s="21" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="F300" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -7072,13 +7062,13 @@
         <v>38</v>
       </c>
       <c r="B301" s="21" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C301" s="21" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F301" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
@@ -7086,13 +7076,13 @@
         <v>38</v>
       </c>
       <c r="B302" s="21" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C302" s="21" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F302" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
@@ -7100,13 +7090,13 @@
         <v>38</v>
       </c>
       <c r="B303" s="21" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C303" s="21" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F303" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -7114,13 +7104,13 @@
         <v>38</v>
       </c>
       <c r="B304" s="21" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C304" s="21" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F304" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -7128,13 +7118,13 @@
         <v>38</v>
       </c>
       <c r="B305" s="21" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C305" s="21" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="F305" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -7142,13 +7132,13 @@
         <v>38</v>
       </c>
       <c r="B306" s="21" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C306" s="21" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F306" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -7156,13 +7146,13 @@
         <v>38</v>
       </c>
       <c r="B307" s="21" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C307" s="21" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F307" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
@@ -7170,13 +7160,13 @@
         <v>38</v>
       </c>
       <c r="B308" s="21" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C308" s="21" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F308" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -7184,13 +7174,13 @@
         <v>38</v>
       </c>
       <c r="B309" s="21" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C309" s="21" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F309" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -7198,13 +7188,13 @@
         <v>38</v>
       </c>
       <c r="B310" s="21" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C310" s="21" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F310" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
@@ -7212,13 +7202,13 @@
         <v>38</v>
       </c>
       <c r="B311" s="21" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C311" s="21" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F311" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
@@ -7226,13 +7216,13 @@
         <v>38</v>
       </c>
       <c r="B312" s="21" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C312" s="21" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F312" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -7240,13 +7230,13 @@
         <v>38</v>
       </c>
       <c r="B313" s="21" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C313" s="21" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F313" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -7254,13 +7244,13 @@
         <v>38</v>
       </c>
       <c r="B314" s="21" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C314" s="21" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F314" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -7268,13 +7258,13 @@
         <v>38</v>
       </c>
       <c r="B315" s="21" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C315" s="21" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="F315" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -7282,13 +7272,13 @@
         <v>38</v>
       </c>
       <c r="B316" s="21" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C316" s="21" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="F316" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -7296,13 +7286,13 @@
         <v>38</v>
       </c>
       <c r="B317" s="21" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C317" s="21" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F317" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -7310,13 +7300,13 @@
         <v>38</v>
       </c>
       <c r="B318" s="21" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C318" s="21" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F318" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -7324,13 +7314,13 @@
         <v>38</v>
       </c>
       <c r="B319" s="21" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C319" s="21" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F319" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
@@ -7338,13 +7328,13 @@
         <v>38</v>
       </c>
       <c r="B320" s="21" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C320" s="21" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F320" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
@@ -7352,13 +7342,13 @@
         <v>38</v>
       </c>
       <c r="B321" s="21" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C321" s="21" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F321" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -7366,13 +7356,13 @@
         <v>38</v>
       </c>
       <c r="B322" s="21" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C322" s="21" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F322" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -7380,13 +7370,13 @@
         <v>38</v>
       </c>
       <c r="B323" s="21" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C323" s="21" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F323" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -7394,13 +7384,13 @@
         <v>38</v>
       </c>
       <c r="B324" s="21" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C324" s="21" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F324" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
@@ -7408,13 +7398,13 @@
         <v>38</v>
       </c>
       <c r="B325" s="21" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C325" s="21" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F325" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -7422,13 +7412,13 @@
         <v>38</v>
       </c>
       <c r="B326" s="21" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C326" s="21" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F326" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -7436,13 +7426,13 @@
         <v>38</v>
       </c>
       <c r="B327" s="21" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C327" s="21" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F327" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -7450,13 +7440,13 @@
         <v>38</v>
       </c>
       <c r="B328" s="21" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C328" s="21" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F328" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -7464,13 +7454,13 @@
         <v>38</v>
       </c>
       <c r="B329" s="21" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C329" s="21" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F329" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -7478,13 +7468,13 @@
         <v>38</v>
       </c>
       <c r="B330" s="21" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C330" s="21" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F330" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -7492,13 +7482,13 @@
         <v>38</v>
       </c>
       <c r="B331" s="21" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C331" s="21" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="F331" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -7506,13 +7496,13 @@
         <v>38</v>
       </c>
       <c r="B332" s="21" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C332" s="21" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F332" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -7520,13 +7510,13 @@
         <v>38</v>
       </c>
       <c r="B333" s="21" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C333" s="21" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F333" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -7534,13 +7524,13 @@
         <v>38</v>
       </c>
       <c r="B334" s="21" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C334" s="21" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F334" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
@@ -7548,13 +7538,13 @@
         <v>38</v>
       </c>
       <c r="B335" s="21" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C335" s="21" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="F335" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
@@ -7562,13 +7552,13 @@
         <v>38</v>
       </c>
       <c r="B336" s="21" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C336" s="21" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F336" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -7576,13 +7566,13 @@
         <v>38</v>
       </c>
       <c r="B337" s="21" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C337" s="21" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F337" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
@@ -7590,13 +7580,13 @@
         <v>38</v>
       </c>
       <c r="B338" s="21" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C338" s="21" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="F338" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -7604,13 +7594,13 @@
         <v>38</v>
       </c>
       <c r="B339" s="21" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C339" s="21" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F339" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -7618,13 +7608,13 @@
         <v>38</v>
       </c>
       <c r="B340" s="21" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C340" s="21" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="F340" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -7632,13 +7622,13 @@
         <v>38</v>
       </c>
       <c r="B341" s="21" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C341" s="21" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F341" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -7646,13 +7636,13 @@
         <v>38</v>
       </c>
       <c r="B342" s="21" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C342" s="21" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="F342" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
@@ -7660,13 +7650,13 @@
         <v>38</v>
       </c>
       <c r="B343" s="21" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C343" s="21" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="F343" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -7674,13 +7664,13 @@
         <v>38</v>
       </c>
       <c r="B344" s="21" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C344" s="21" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F344" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -7688,13 +7678,13 @@
         <v>38</v>
       </c>
       <c r="B345" s="21" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C345" s="21" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F345" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -7702,13 +7692,13 @@
         <v>38</v>
       </c>
       <c r="B346" s="21" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C346" s="21" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F346" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -7716,13 +7706,13 @@
         <v>38</v>
       </c>
       <c r="B347" s="21" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C347" s="21" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F347" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
@@ -7730,13 +7720,13 @@
         <v>38</v>
       </c>
       <c r="B348" s="21" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C348" s="21" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F348" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -7744,13 +7734,13 @@
         <v>38</v>
       </c>
       <c r="B349" s="21" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C349" s="21" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="F349" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
@@ -7758,13 +7748,13 @@
         <v>38</v>
       </c>
       <c r="B350" s="21" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C350" s="21" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F350" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
@@ -7772,13 +7762,13 @@
         <v>38</v>
       </c>
       <c r="B351" s="21" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C351" s="21" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F351" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
@@ -7786,13 +7776,13 @@
         <v>38</v>
       </c>
       <c r="B352" s="21" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C352" s="21" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F352" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
@@ -7800,13 +7790,13 @@
         <v>38</v>
       </c>
       <c r="B353" s="21" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C353" s="21" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F353" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
@@ -7814,13 +7804,13 @@
         <v>38</v>
       </c>
       <c r="B354" s="21" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C354" s="21" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="F354" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
@@ -7828,13 +7818,13 @@
         <v>38</v>
       </c>
       <c r="B355" s="21" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C355" s="21" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="F355" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
@@ -7842,13 +7832,13 @@
         <v>38</v>
       </c>
       <c r="B356" s="21" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C356" s="21" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="F356" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
@@ -7856,13 +7846,13 @@
         <v>38</v>
       </c>
       <c r="B357" s="21" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C357" s="21" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F357" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
@@ -7870,13 +7860,13 @@
         <v>38</v>
       </c>
       <c r="B358" s="21" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C358" s="21" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F358" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
@@ -7884,13 +7874,13 @@
         <v>38</v>
       </c>
       <c r="B359" s="21" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C359" s="21" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F359" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
@@ -7898,13 +7888,13 @@
         <v>38</v>
       </c>
       <c r="B360" s="21" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C360" s="21" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="F360" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
@@ -7912,13 +7902,13 @@
         <v>38</v>
       </c>
       <c r="B361" s="21" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C361" s="21" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="F361" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
@@ -7926,13 +7916,13 @@
         <v>38</v>
       </c>
       <c r="B362" s="21" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C362" s="21" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F362" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
@@ -7940,13 +7930,13 @@
         <v>38</v>
       </c>
       <c r="B363" s="21" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C363" s="21" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="F363" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
@@ -7954,13 +7944,13 @@
         <v>38</v>
       </c>
       <c r="B364" s="21" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C364" s="21" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="F364" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
@@ -7968,13 +7958,13 @@
         <v>38</v>
       </c>
       <c r="B365" s="21" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C365" s="21" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="F365" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
@@ -7982,13 +7972,13 @@
         <v>38</v>
       </c>
       <c r="B366" s="21" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C366" s="21" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F366" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
@@ -7996,13 +7986,13 @@
         <v>38</v>
       </c>
       <c r="B367" s="21" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C367" s="21" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="F367" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
@@ -8010,13 +8000,13 @@
         <v>38</v>
       </c>
       <c r="B368" s="21" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C368" s="21" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="F368" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
@@ -8024,13 +8014,13 @@
         <v>38</v>
       </c>
       <c r="B369" s="21" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C369" s="21" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="F369" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
@@ -8038,13 +8028,13 @@
         <v>38</v>
       </c>
       <c r="B370" s="21" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C370" s="21" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="F370" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
@@ -8052,13 +8042,13 @@
         <v>38</v>
       </c>
       <c r="B371" s="21" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C371" s="21" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F371" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
@@ -8066,13 +8056,13 @@
         <v>38</v>
       </c>
       <c r="B372" s="21" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C372" s="21" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="F372" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
@@ -8080,13 +8070,13 @@
         <v>38</v>
       </c>
       <c r="B373" s="21" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C373" s="21" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F373" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
@@ -8094,13 +8084,13 @@
         <v>38</v>
       </c>
       <c r="B374" s="21" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C374" s="21" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F374" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
@@ -8108,13 +8098,13 @@
         <v>38</v>
       </c>
       <c r="B375" s="21" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C375" s="21" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F375" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
@@ -8122,13 +8112,13 @@
         <v>38</v>
       </c>
       <c r="B376" s="21" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C376" s="21" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="F376" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
@@ -8136,13 +8126,13 @@
         <v>38</v>
       </c>
       <c r="B377" s="21" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C377" s="21" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="F377" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
@@ -8150,13 +8140,13 @@
         <v>38</v>
       </c>
       <c r="B378" s="21" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C378" s="21" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="F378" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
@@ -8164,13 +8154,13 @@
         <v>38</v>
       </c>
       <c r="B379" s="21" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C379" s="21" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="F379" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
@@ -8178,13 +8168,13 @@
         <v>38</v>
       </c>
       <c r="B380" s="21" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C380" s="21" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="F380" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
@@ -8192,13 +8182,13 @@
         <v>38</v>
       </c>
       <c r="B381" s="21" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C381" s="21" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="F381" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
@@ -8206,13 +8196,13 @@
         <v>38</v>
       </c>
       <c r="B382" s="21" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C382" s="21" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="F382" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
@@ -8220,13 +8210,13 @@
         <v>38</v>
       </c>
       <c r="B383" s="21" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C383" s="21" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="F383" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
@@ -8234,13 +8224,13 @@
         <v>38</v>
       </c>
       <c r="B384" s="21" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C384" s="21" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="F384" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
@@ -8248,13 +8238,13 @@
         <v>38</v>
       </c>
       <c r="B385" s="21" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C385" s="21" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="F385" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
@@ -8262,13 +8252,13 @@
         <v>38</v>
       </c>
       <c r="B386" s="21" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C386" s="21" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="F386" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
@@ -8276,13 +8266,13 @@
         <v>38</v>
       </c>
       <c r="B387" s="21" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C387" s="21" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="F387" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
@@ -8290,13 +8280,13 @@
         <v>38</v>
       </c>
       <c r="B388" s="21" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C388" s="21" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="F388" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
@@ -8304,13 +8294,13 @@
         <v>38</v>
       </c>
       <c r="B389" s="21" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C389" s="21" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="F389" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
@@ -8318,13 +8308,13 @@
         <v>38</v>
       </c>
       <c r="B390" s="21" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C390" s="21" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F390" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
@@ -8332,13 +8322,13 @@
         <v>38</v>
       </c>
       <c r="B391" s="21" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C391" s="21" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F391" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
@@ -8346,13 +8336,13 @@
         <v>38</v>
       </c>
       <c r="B392" s="21" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C392" s="21" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F392" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
@@ -8360,13 +8350,13 @@
         <v>38</v>
       </c>
       <c r="B393" s="21" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C393" s="21" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="F393" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
@@ -8374,13 +8364,13 @@
         <v>38</v>
       </c>
       <c r="B394" s="21" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C394" s="21" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="F394" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
@@ -8388,13 +8378,13 @@
         <v>38</v>
       </c>
       <c r="B395" s="21" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C395" s="21" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F395" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
@@ -8402,13 +8392,13 @@
         <v>38</v>
       </c>
       <c r="B396" s="21" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C396" s="21" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="F396" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
@@ -8416,13 +8406,13 @@
         <v>38</v>
       </c>
       <c r="B397" s="21" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C397" s="21" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F397" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
@@ -8430,13 +8420,13 @@
         <v>38</v>
       </c>
       <c r="B398" s="21" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C398" s="21" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F398" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
@@ -8444,13 +8434,13 @@
         <v>38</v>
       </c>
       <c r="B399" s="21" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C399" s="21" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="F399" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
@@ -8458,13 +8448,13 @@
         <v>38</v>
       </c>
       <c r="B400" s="21" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C400" s="21" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="F400" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
@@ -8472,13 +8462,13 @@
         <v>38</v>
       </c>
       <c r="B401" s="21" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C401" s="21" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="F401" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
@@ -8486,13 +8476,13 @@
         <v>38</v>
       </c>
       <c r="B402" s="21" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C402" s="21" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="F402" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
@@ -8500,13 +8490,13 @@
         <v>38</v>
       </c>
       <c r="B403" s="21" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C403" s="21" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F403" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
@@ -8514,13 +8504,13 @@
         <v>38</v>
       </c>
       <c r="B404" s="21" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C404" s="21" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="F404" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
@@ -8528,13 +8518,13 @@
         <v>38</v>
       </c>
       <c r="B405" s="21" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C405" s="21" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F405" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
@@ -8542,13 +8532,13 @@
         <v>38</v>
       </c>
       <c r="B406" s="21" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C406" s="21" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="F406" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -8582,12 +8572,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>164</v>
+        <v>535</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>163</v>
+        <v>536</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>21</v>
